--- a/Excel02.xlsx
+++ b/Excel02.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LinhLT\Job\File test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LinhLT\Job\02.Server_GIT\5.2.0_Github_8302_repo05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF2A17FE-B3AF-4EA1-8F3A-D8D7B59C9265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD2E80EC-F4F3-4654-947C-36BAA4F43432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-5625" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>A1</t>
   </si>
@@ -55,6 +55,9 @@
   </si>
   <si>
     <t>bbbb</t>
+  </si>
+  <si>
+    <t>A3</t>
   </si>
 </sst>
 </file>
@@ -372,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -409,6 +412,11 @@
         <v>9</v>
       </c>
     </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
